--- a/exports/trend_1d/JSWENERGY_full_report.xlsx
+++ b/exports/trend_1d/JSWENERGY_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:U77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>11.87</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42038</v>
+        <v>42039</v>
       </c>
       <c r="H2" t="n">
-        <v>112.85</v>
+        <v>107.65</v>
       </c>
       <c r="I2" t="n">
         <v>110.5576793438046</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>6.61</v>
+        <v>1.7</v>
       </c>
       <c r="L2" t="n">
         <v>3.54</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>17.99</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42086</v>
+        <v>42087</v>
       </c>
       <c r="H3" t="n">
-        <v>118</v>
+        <v>121.6</v>
       </c>
       <c r="I3" t="n">
         <v>120.0566290825298</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K3" t="n">
-        <v>-9.609999999999999</v>
+        <v>-12.96</v>
       </c>
       <c r="L3" t="n">
-        <v>13.52</v>
+        <v>13.79</v>
       </c>
       <c r="M3" t="n">
         <v>1.38</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>13.27</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42118</v>
+        <v>42121</v>
       </c>
       <c r="H4" t="n">
-        <v>114.75</v>
+        <v>106.6</v>
       </c>
       <c r="I4" t="n">
         <v>109.049295211259</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.63</v>
+        <v>-12.34</v>
       </c>
       <c r="L4" t="n">
-        <v>9.17</v>
+        <v>13.16</v>
       </c>
       <c r="M4" t="n">
-        <v>0.61</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>7.1</v>
       </c>
       <c r="O4" t="n">
         <v>3.05</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>13.66</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42256</v>
+        <v>42257</v>
       </c>
       <c r="H5" t="n">
-        <v>78</v>
+        <v>81.95</v>
       </c>
       <c r="I5" t="n">
         <v>80.44603862481654</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K5" t="n">
-        <v>26.83</v>
+        <v>23.12</v>
       </c>
       <c r="L5" t="n">
         <v>12.85</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>26.74</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42345</v>
+        <v>42346</v>
       </c>
       <c r="H6" t="n">
-        <v>83.8</v>
+        <v>78.95</v>
       </c>
       <c r="I6" t="n">
         <v>81.32972334934068</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K6" t="n">
-        <v>2.26</v>
+        <v>-3.66</v>
       </c>
       <c r="L6" t="n">
         <v>9.4</v>
@@ -783,7 +854,7 @@
         <v>3.96</v>
       </c>
       <c r="N6" t="n">
-        <v>5.48</v>
+        <v>5.79</v>
       </c>
       <c r="O6" t="n">
         <v>5.06</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>14.91</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42369</v>
+        <v>42370</v>
       </c>
       <c r="H7" t="n">
-        <v>85.05</v>
+        <v>86.65000000000001</v>
       </c>
       <c r="I7" t="n">
         <v>85.72885565225245</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.73</v>
+        <v>-9.75</v>
       </c>
       <c r="L7" t="n">
-        <v>9.44</v>
+        <v>10.2</v>
       </c>
       <c r="M7" t="n">
         <v>1.7</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>11.06</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42383</v>
+        <v>42384</v>
       </c>
       <c r="H8" t="n">
-        <v>77.90000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="I8" t="n">
         <v>77.32957320586347</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>-10.1</v>
+        <v>-16.56</v>
       </c>
       <c r="L8" t="n">
-        <v>13.56</v>
+        <v>18.12</v>
       </c>
       <c r="M8" t="n">
         <v>2.25</v>
       </c>
       <c r="N8" t="n">
-        <v>5.29</v>
+        <v>7.19</v>
       </c>
       <c r="O8" t="n">
         <v>1.88</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>22.44</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42450</v>
+        <v>42451</v>
       </c>
       <c r="H9" t="n">
-        <v>71.65000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="I9" t="n">
         <v>72.26523842599192</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>8.85</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.19</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42641</v>
+        <v>42642</v>
       </c>
       <c r="H10" t="n">
-        <v>77.59999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>75.46664529568552</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K10" t="n">
-        <v>7.33</v>
+        <v>0.83</v>
       </c>
       <c r="L10" t="n">
         <v>12.17</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>13.82</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42734</v>
+        <v>42737</v>
       </c>
       <c r="H11" t="n">
-        <v>60.85</v>
+        <v>62.25</v>
       </c>
       <c r="I11" t="n">
         <v>62.140989108404</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K11" t="n">
-        <v>16.53</v>
+        <v>14.61</v>
       </c>
       <c r="L11" t="n">
         <v>7.61</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>12</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42878</v>
+        <v>42879</v>
       </c>
       <c r="H12" t="n">
-        <v>63.55</v>
+        <v>62.1</v>
       </c>
       <c r="I12" t="n">
         <v>62.16586078896513</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K12" t="n">
-        <v>2.09</v>
+        <v>-0.24</v>
       </c>
       <c r="L12" t="n">
         <v>5.7</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>15.39</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42941</v>
+        <v>42942</v>
       </c>
       <c r="H13" t="n">
-        <v>66.45</v>
+        <v>68</v>
       </c>
       <c r="I13" t="n">
         <v>67.76678089752795</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K13" t="n">
-        <v>-7</v>
+        <v>-9.5</v>
       </c>
       <c r="L13" t="n">
-        <v>10.71</v>
+        <v>11.43</v>
       </c>
       <c r="M13" t="n">
         <v>1.24</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>10.32</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42965</v>
+        <v>42968</v>
       </c>
       <c r="H14" t="n">
-        <v>63.95</v>
+        <v>62.8</v>
       </c>
       <c r="I14" t="n">
         <v>63.23574738441039</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.96</v>
+        <v>-7.65</v>
       </c>
       <c r="L14" t="n">
         <v>8.380000000000001</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>14.82</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42985</v>
+        <v>42986</v>
       </c>
       <c r="H15" t="n">
-        <v>67.15000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I15" t="n">
         <v>69.69361796577536</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.93</v>
+        <v>-14.81</v>
       </c>
       <c r="L15" t="n">
-        <v>10.67</v>
+        <v>18.39</v>
       </c>
       <c r="M15" t="n">
         <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>4.86</v>
+        <v>7.37</v>
       </c>
       <c r="O15" t="n">
         <v>-1.8</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>14.18</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43004</v>
+        <v>43005</v>
       </c>
       <c r="H16" t="n">
-        <v>73.05</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I16" t="n">
         <v>70.67143372700338</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K16" t="n">
-        <v>1.32</v>
+        <v>-4.44</v>
       </c>
       <c r="L16" t="n">
         <v>7</v>
@@ -1353,7 +1544,7 @@
         <v>0.52</v>
       </c>
       <c r="N16" t="n">
-        <v>4.62</v>
+        <v>5.68</v>
       </c>
       <c r="O16" t="n">
         <v>7.37</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>20.16</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43033</v>
+        <v>43034</v>
       </c>
       <c r="H17" t="n">
-        <v>81.5</v>
+        <v>83.7</v>
       </c>
       <c r="I17" t="n">
         <v>82.79230784854178</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K17" t="n">
-        <v>-18.29</v>
+        <v>-21.48</v>
       </c>
       <c r="L17" t="n">
-        <v>22.35</v>
+        <v>22.5</v>
       </c>
       <c r="M17" t="n">
         <v>3.9</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>12.97</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H18" t="n">
-        <v>87.34999999999999</v>
+        <v>84.05</v>
       </c>
       <c r="I18" t="n">
         <v>85.92371049416798</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K18" t="n">
-        <v>4.36</v>
+        <v>0.42</v>
       </c>
       <c r="L18" t="n">
         <v>7.47</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>15.32</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43194</v>
+        <v>43195</v>
       </c>
       <c r="H19" t="n">
-        <v>80.95</v>
+        <v>83</v>
       </c>
       <c r="I19" t="n">
         <v>81.17001218586257</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K19" t="n">
-        <v>3.69</v>
+        <v>1.25</v>
       </c>
       <c r="L19" t="n">
         <v>5</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>11.73</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43223</v>
+        <v>43224</v>
       </c>
       <c r="H20" t="n">
-        <v>81.8</v>
+        <v>75.25</v>
       </c>
       <c r="I20" t="n">
         <v>78.08818821896182</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.45</v>
+        <v>-9.34</v>
       </c>
       <c r="L20" t="n">
-        <v>5.3</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>1.25</v>
+        <v>4.89</v>
       </c>
       <c r="N20" t="n">
-        <v>3.24</v>
+        <v>8.01</v>
       </c>
       <c r="O20" t="n">
         <v>2.53</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>15.69</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43249</v>
+        <v>43250</v>
       </c>
       <c r="H21" t="n">
-        <v>76.65000000000001</v>
+        <v>81.75</v>
       </c>
       <c r="I21" t="n">
         <v>78.22054793637028</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.86</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>5.12</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="M21" t="n">
         <v>1.42</v>
       </c>
       <c r="N21" t="n">
-        <v>6.06</v>
+        <v>6.65</v>
       </c>
       <c r="O21" t="n">
         <v>-8.01</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>15.75</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43255</v>
+        <v>43256</v>
       </c>
       <c r="H22" t="n">
-        <v>74.25</v>
+        <v>71.25</v>
       </c>
       <c r="I22" t="n">
         <v>71.53478735288587</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K22" t="n">
-        <v>-9.17</v>
+        <v>-12.84</v>
       </c>
       <c r="L22" t="n">
-        <v>10.4</v>
+        <v>13.58</v>
       </c>
       <c r="M22" t="n">
         <v>1.52</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>16.95</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43341</v>
+        <v>43342</v>
       </c>
       <c r="H23" t="n">
-        <v>68.45</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I23" t="n">
         <v>70.16297789940224</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K23" t="n">
-        <v>3.93</v>
+        <v>1.19</v>
       </c>
       <c r="L23" t="n">
         <v>6.95</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>10</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43362</v>
+        <v>43364</v>
       </c>
       <c r="H24" t="n">
-        <v>67.59999999999999</v>
+        <v>63.65</v>
       </c>
       <c r="I24" t="n">
         <v>65.84888015541136</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.98</v>
+        <v>-9.59</v>
       </c>
       <c r="L24" t="n">
-        <v>8.1</v>
+        <v>11.93</v>
       </c>
       <c r="M24" t="n">
         <v>1.87</v>
       </c>
       <c r="N24" t="n">
-        <v>3.06</v>
+        <v>5.84</v>
       </c>
       <c r="O24" t="n">
         <v>2.85</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>16.4</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43409</v>
+        <v>43410</v>
       </c>
       <c r="H25" t="n">
-        <v>67.95</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>67.97263793285377</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.76</v>
+        <v>-6.99</v>
       </c>
       <c r="L25" t="n">
         <v>8.09</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>13.89</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43493</v>
+        <v>43494</v>
       </c>
       <c r="H26" t="n">
-        <v>64.95</v>
+        <v>64.2</v>
       </c>
       <c r="I26" t="n">
         <v>64.52589912292399</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.63</v>
+        <v>-5.73</v>
       </c>
       <c r="L26" t="n">
         <v>7.78</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>10.27</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43530</v>
+        <v>43531</v>
       </c>
       <c r="H27" t="n">
-        <v>68.5</v>
+        <v>70.3</v>
       </c>
       <c r="I27" t="n">
         <v>70.21298383717762</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K27" t="n">
-        <v>-6.7</v>
+        <v>-9.5</v>
       </c>
       <c r="L27" t="n">
-        <v>9.58</v>
+        <v>13.08</v>
       </c>
       <c r="M27" t="n">
         <v>1.22</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.09</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43605</v>
+        <v>43606</v>
       </c>
       <c r="H28" t="n">
-        <v>68.15000000000001</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="I28" t="n">
         <v>66.84706566845533</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.06</v>
+        <v>-5.62</v>
       </c>
       <c r="L28" t="n">
         <v>9.1</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>10.48</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43609</v>
+        <v>43612</v>
       </c>
       <c r="H29" t="n">
-        <v>71.55</v>
+        <v>72.8</v>
       </c>
       <c r="I29" t="n">
         <v>72.28523243717602</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>-7.84</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>8.52</v>
+        <v>11.98</v>
       </c>
       <c r="M29" t="n">
         <v>0.75</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>10.38</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43630</v>
+        <v>43633</v>
       </c>
       <c r="H30" t="n">
-        <v>68.8</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="I30" t="n">
         <v>66.49470399796881</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K30" t="n">
-        <v>-5.49</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>6.25</v>
+        <v>9.48</v>
       </c>
       <c r="M30" t="n">
         <v>0.63</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>12.73</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43754</v>
+        <v>43755</v>
       </c>
       <c r="H31" t="n">
-        <v>64.7</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I31" t="n">
         <v>66.24764188522099</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K31" t="n">
-        <v>2.19</v>
+        <v>-0.38</v>
       </c>
       <c r="L31" t="n">
         <v>11.11</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>13.59</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43833</v>
+        <v>43836</v>
       </c>
       <c r="H32" t="n">
-        <v>70.2</v>
+        <v>67.05</v>
       </c>
       <c r="I32" t="n">
         <v>67.75788655470612</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K32" t="n">
-        <v>5.72</v>
+        <v>0.98</v>
       </c>
       <c r="L32" t="n">
         <v>4.82</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>11.48</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43987</v>
+        <v>43990</v>
       </c>
       <c r="H33" t="n">
-        <v>44.3</v>
+        <v>45.8</v>
       </c>
       <c r="I33" t="n">
         <v>45.52347389138679</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K33" t="n">
-        <v>33.93</v>
+        <v>31.69</v>
       </c>
       <c r="L33" t="n">
         <v>8.130000000000001</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>6</v>
+      </c>
+      <c r="U33" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>14.71</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44027</v>
+        <v>44028</v>
       </c>
       <c r="H34" t="n">
-        <v>43.95</v>
+        <v>43.6</v>
       </c>
       <c r="I34" t="n">
         <v>43.76642316535776</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.04</v>
+        <v>-4.8</v>
       </c>
       <c r="L34" t="n">
-        <v>5.35</v>
+        <v>6.11</v>
       </c>
       <c r="M34" t="n">
         <v>6.05</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>13.75</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44050</v>
+        <v>44053</v>
       </c>
       <c r="H35" t="n">
-        <v>48.1</v>
+        <v>50.85</v>
       </c>
       <c r="I35" t="n">
         <v>49.5928803504062</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K35" t="n">
-        <v>-10.32</v>
+        <v>-16.63</v>
       </c>
       <c r="L35" t="n">
-        <v>16.17</v>
+        <v>17.89</v>
       </c>
       <c r="M35" t="n">
         <v>1.86</v>
       </c>
       <c r="N35" t="n">
-        <v>5.48</v>
+        <v>5.72</v>
       </c>
       <c r="O35" t="n">
         <v>-0.8</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>14.03</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44496</v>
+        <v>44497</v>
       </c>
       <c r="H36" t="n">
-        <v>366.55</v>
+        <v>348.25</v>
       </c>
       <c r="I36" t="n">
         <v>349.3006802417411</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K36" t="n">
-        <v>620.85</v>
+        <v>584.86</v>
       </c>
       <c r="L36" t="n">
         <v>4.62</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>304</v>
+        <v>305</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>15</v>
+      </c>
+      <c r="U36" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>18.88</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44601</v>
+        <v>44602</v>
       </c>
       <c r="H37" t="n">
-        <v>309.6</v>
+        <v>325.05</v>
       </c>
       <c r="I37" t="n">
         <v>324.3413269891468</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K37" t="n">
-        <v>11.1</v>
+        <v>6.66</v>
       </c>
       <c r="L37" t="n">
         <v>6.16</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>15.29</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44648</v>
+        <v>44649</v>
       </c>
       <c r="H38" t="n">
-        <v>302.5</v>
+        <v>294.25</v>
       </c>
       <c r="I38" t="n">
         <v>294.8962902142921</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K38" t="n">
-        <v>-6.94</v>
+        <v>-9.48</v>
       </c>
       <c r="L38" t="n">
         <v>11.09</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,25 +3110,25 @@
         <v>14.44</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44655</v>
+        <v>44656</v>
       </c>
       <c r="H39" t="n">
-        <v>324.65</v>
+        <v>340.85</v>
       </c>
       <c r="I39" t="n">
         <v>334.9201733166026</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K39" t="n">
-        <v>-10.33</v>
+        <v>-15.84</v>
       </c>
       <c r="L39" t="n">
-        <v>10.33</v>
+        <v>15.84</v>
       </c>
       <c r="M39" t="n">
-        <v>1.75</v>
+        <v>4.99</v>
       </c>
       <c r="N39" t="n">
         <v>5</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,25 +3179,25 @@
         <v>13.34</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H40" t="n">
-        <v>306.9</v>
+        <v>301.35</v>
       </c>
       <c r="I40" t="n">
         <v>301.517761786977</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K40" t="n">
-        <v>-9.960000000000001</v>
+        <v>-11.59</v>
       </c>
       <c r="L40" t="n">
-        <v>11.69</v>
+        <v>13.66</v>
       </c>
       <c r="M40" t="n">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="N40" t="n">
         <v>4.99</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>16.87</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44769</v>
+        <v>44770</v>
       </c>
       <c r="H41" t="n">
-        <v>227.75</v>
+        <v>242.8</v>
       </c>
       <c r="I41" t="n">
         <v>241.978945247647</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K41" t="n">
-        <v>24.42</v>
+        <v>19.43</v>
       </c>
       <c r="L41" t="n">
         <v>7.85</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>16.97</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H42" t="n">
-        <v>319.1</v>
+        <v>296.15</v>
       </c>
       <c r="I42" t="n">
         <v>309.4701438019204</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K42" t="n">
-        <v>31.43</v>
+        <v>21.97</v>
       </c>
       <c r="L42" t="n">
         <v>6.3</v>
@@ -2835,7 +3338,7 @@
         <v>3.27</v>
       </c>
       <c r="N42" t="n">
-        <v>3.78</v>
+        <v>7.19</v>
       </c>
       <c r="O42" t="n">
         <v>6.61</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>20.05</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44840</v>
+        <v>44841</v>
       </c>
       <c r="H43" t="n">
-        <v>330.65</v>
+        <v>345</v>
       </c>
       <c r="I43" t="n">
         <v>340.3832375263445</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K43" t="n">
-        <v>-11.65</v>
+        <v>-16.5</v>
       </c>
       <c r="L43" t="n">
-        <v>12.85</v>
+        <v>17.42</v>
       </c>
       <c r="M43" t="n">
         <v>2.38</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>17.44</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44882</v>
+        <v>44883</v>
       </c>
       <c r="H44" t="n">
-        <v>309.75</v>
+        <v>304.9</v>
       </c>
       <c r="I44" t="n">
         <v>305.4388881478075</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K44" t="n">
-        <v>-10.22</v>
+        <v>-11.62</v>
       </c>
       <c r="L44" t="n">
-        <v>10.59</v>
+        <v>12.2</v>
       </c>
       <c r="M44" t="n">
         <v>1.52</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>11.29</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44925</v>
+        <v>44928</v>
       </c>
       <c r="H45" t="n">
-        <v>287.6</v>
+        <v>293.55</v>
       </c>
       <c r="I45" t="n">
         <v>292.9369080190029</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K45" t="n">
-        <v>5.67</v>
+        <v>3.72</v>
       </c>
       <c r="L45" t="n">
         <v>4.89</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>12.29</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44946</v>
+        <v>44949</v>
       </c>
       <c r="H46" t="n">
-        <v>262.35</v>
+        <v>246.85</v>
       </c>
       <c r="I46" t="n">
         <v>258.3442886389258</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K46" t="n">
-        <v>-10.63</v>
+        <v>-15.91</v>
       </c>
       <c r="L46" t="n">
-        <v>10.82</v>
+        <v>16.25</v>
       </c>
       <c r="M46" t="n">
-        <v>0.11</v>
+        <v>2.8</v>
       </c>
       <c r="N46" t="n">
-        <v>2.13</v>
+        <v>5.91</v>
       </c>
       <c r="O46" t="n">
         <v>2.07</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>12.79</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44984</v>
+        <v>44985</v>
       </c>
       <c r="H47" t="n">
-        <v>208.25</v>
+        <v>234.65</v>
       </c>
       <c r="I47" t="n">
         <v>233.9757638731302</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K47" t="n">
-        <v>15.64</v>
+        <v>4.94</v>
       </c>
       <c r="L47" t="n">
         <v>3.3</v>
@@ -3120,7 +3683,7 @@
         <v>0.97</v>
       </c>
       <c r="N47" t="n">
-        <v>5.51</v>
+        <v>12.68</v>
       </c>
       <c r="O47" t="n">
         <v>-5.91</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>18.76</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45009</v>
+        <v>45012</v>
       </c>
       <c r="H48" t="n">
-        <v>236.7</v>
+        <v>227.1</v>
       </c>
       <c r="I48" t="n">
         <v>230.5687588543498</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K48" t="n">
-        <v>0.87</v>
+        <v>-3.22</v>
       </c>
       <c r="L48" t="n">
         <v>11.29</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>18.57</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45051</v>
+        <v>45054</v>
       </c>
       <c r="H49" t="n">
-        <v>260.45</v>
+        <v>263.1</v>
       </c>
       <c r="I49" t="n">
         <v>262.2360718552553</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K49" t="n">
-        <v>-14.69</v>
+        <v>-15.85</v>
       </c>
       <c r="L49" t="n">
-        <v>17.15</v>
+        <v>20.21</v>
       </c>
       <c r="M49" t="n">
         <v>3.11</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.81</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45222</v>
+        <v>45224</v>
       </c>
       <c r="H50" t="n">
-        <v>376.35</v>
+        <v>366.2</v>
       </c>
       <c r="I50" t="n">
         <v>374.6081837351602</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K50" t="n">
-        <v>43.04</v>
+        <v>39.19</v>
       </c>
       <c r="L50" t="n">
         <v>8.779999999999999</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>6</v>
+      </c>
+      <c r="U50" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>16.9</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="H51" t="n">
-        <v>415.2</v>
+        <v>439</v>
       </c>
       <c r="I51" t="n">
         <v>428.1060526214911</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K51" t="n">
-        <v>-13.38</v>
+        <v>-19.88</v>
       </c>
       <c r="L51" t="n">
-        <v>18.73</v>
+        <v>20.96</v>
       </c>
       <c r="M51" t="n">
         <v>2.21</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>12.56</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45279</v>
+        <v>45280</v>
       </c>
       <c r="H52" t="n">
-        <v>431.35</v>
+        <v>405.05</v>
       </c>
       <c r="I52" t="n">
         <v>407.6029240877877</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.74</v>
+        <v>-7.73</v>
       </c>
       <c r="L52" t="n">
-        <v>5.57</v>
+        <v>8.77</v>
       </c>
       <c r="M52" t="n">
         <v>4.65</v>
       </c>
       <c r="N52" t="n">
-        <v>3.6</v>
+        <v>6.1</v>
       </c>
       <c r="O52" t="n">
         <v>5.73</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>18.85</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45299</v>
+        <v>45300</v>
       </c>
       <c r="H53" t="n">
-        <v>419.45</v>
+        <v>454.85</v>
       </c>
       <c r="I53" t="n">
         <v>453.7371529859028</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.56</v>
+        <v>-12.29</v>
       </c>
       <c r="L53" t="n">
-        <v>8.789999999999999</v>
+        <v>13.16</v>
       </c>
       <c r="M53" t="n">
         <v>2.61</v>
       </c>
       <c r="N53" t="n">
-        <v>3.66</v>
+        <v>8.44</v>
       </c>
       <c r="O53" t="n">
         <v>-6.1</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>14.6</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H54" t="n">
-        <v>509.3</v>
+        <v>461.05</v>
       </c>
       <c r="I54" t="n">
         <v>464.5374301866368</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K54" t="n">
-        <v>11.97</v>
+        <v>1.36</v>
       </c>
       <c r="L54" t="n">
         <v>7.64</v>
@@ -3519,7 +4166,7 @@
         <v>2.92</v>
       </c>
       <c r="N54" t="n">
-        <v>5.04</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O54" t="n">
         <v>8.44</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>18.89</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="H55" t="n">
-        <v>518.45</v>
+        <v>542.2</v>
       </c>
       <c r="I55" t="n">
         <v>533.7574545545476</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K55" t="n">
-        <v>-12.45</v>
+        <v>-17.6</v>
       </c>
       <c r="L55" t="n">
-        <v>16.66</v>
+        <v>17.77</v>
       </c>
       <c r="M55" t="n">
         <v>1.61</v>
       </c>
       <c r="N55" t="n">
-        <v>4.41</v>
+        <v>4.58</v>
       </c>
       <c r="O55" t="n">
         <v>-9.470000000000001</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>13.37</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45419</v>
+        <v>45420</v>
       </c>
       <c r="H56" t="n">
-        <v>584.05</v>
+        <v>557.25</v>
       </c>
       <c r="I56" t="n">
         <v>573.6742018784374</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K56" t="n">
-        <v>7.72</v>
+        <v>2.78</v>
       </c>
       <c r="L56" t="n">
         <v>4.18</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>20.57</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45443</v>
+        <v>45446</v>
       </c>
       <c r="H57" t="n">
-        <v>613</v>
+        <v>658.7</v>
       </c>
       <c r="I57" t="n">
         <v>648.7217491545214</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K57" t="n">
-        <v>-10</v>
+        <v>-18.21</v>
       </c>
       <c r="L57" t="n">
-        <v>14.06</v>
+        <v>19.12</v>
       </c>
       <c r="M57" t="n">
-        <v>1.57</v>
+        <v>5.06</v>
       </c>
       <c r="N57" t="n">
-        <v>7.4</v>
+        <v>7.46</v>
       </c>
       <c r="O57" t="n">
         <v>-4.59</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>14.14</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H58" t="n">
-        <v>658.7</v>
+        <v>553.3</v>
       </c>
       <c r="I58" t="n">
         <v>565.5839671684257</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="L58" t="n">
-        <v>2.84</v>
+        <v>19.84</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O58" t="n">
         <v>7.46</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>28.7</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45463</v>
+        <v>45464</v>
       </c>
       <c r="H59" t="n">
-        <v>707.1</v>
+        <v>723.65</v>
       </c>
       <c r="I59" t="n">
         <v>708.4859865935751</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K59" t="n">
-        <v>-27.8</v>
+        <v>-30.79</v>
       </c>
       <c r="L59" t="n">
-        <v>29</v>
+        <v>31.57</v>
       </c>
       <c r="M59" t="n">
         <v>4.05</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>13.25</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45517</v>
+        <v>45518</v>
       </c>
       <c r="H60" t="n">
-        <v>672.55</v>
+        <v>645.95</v>
       </c>
       <c r="I60" t="n">
         <v>668.0131077548344</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K60" t="n">
-        <v>-7.06</v>
+        <v>-10.74</v>
       </c>
       <c r="L60" t="n">
-        <v>7.97</v>
+        <v>11.28</v>
       </c>
       <c r="M60" t="n">
         <v>4.3</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>14.79</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H61" t="n">
-        <v>730.75</v>
+        <v>744.2</v>
       </c>
       <c r="I61" t="n">
         <v>737.4545807277667</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K61" t="n">
-        <v>-13.13</v>
+        <v>-15.21</v>
       </c>
       <c r="L61" t="n">
         <v>16.32</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>10.55</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H62" t="n">
-        <v>723.45</v>
+        <v>708.6</v>
       </c>
       <c r="I62" t="n">
         <v>716.0189276490473</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.79</v>
+        <v>-4.78</v>
       </c>
       <c r="L62" t="n">
-        <v>4.31</v>
+        <v>5.12</v>
       </c>
       <c r="M62" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="N62" t="n">
         <v>4.65</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>11.4</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45604</v>
+        <v>45607</v>
       </c>
       <c r="H63" t="n">
-        <v>712.05</v>
+        <v>739.25</v>
       </c>
       <c r="I63" t="n">
         <v>735.80933355741</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.49</v>
+        <v>-4.33</v>
       </c>
       <c r="L63" t="n">
-        <v>4.64</v>
+        <v>6.07</v>
       </c>
       <c r="M63" t="n">
         <v>1.6</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>12.69</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45621</v>
+        <v>45622</v>
       </c>
       <c r="H64" t="n">
-        <v>675.05</v>
+        <v>657.4</v>
       </c>
       <c r="I64" t="n">
         <v>671.7014928776848</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K64" t="n">
-        <v>-8.68</v>
+        <v>-11.07</v>
       </c>
       <c r="L64" t="n">
-        <v>9.94</v>
+        <v>11.94</v>
       </c>
       <c r="M64" t="n">
         <v>0.83</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>14.66</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45720</v>
+        <v>45721</v>
       </c>
       <c r="H65" t="n">
-        <v>481.25</v>
+        <v>509.1</v>
       </c>
       <c r="I65" t="n">
         <v>496.6016234457636</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K65" t="n">
-        <v>26.79</v>
+        <v>22.56</v>
       </c>
       <c r="L65" t="n">
         <v>6.62</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>5</v>
+      </c>
+      <c r="U65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -4182,25 +4973,25 @@
         <v>17.12</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H66" t="n">
-        <v>506.4</v>
+        <v>488.4</v>
       </c>
       <c r="I66" t="n">
         <v>502.8969812373062</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.53</v>
+        <v>-4.07</v>
       </c>
       <c r="L66" t="n">
-        <v>5.86</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="M66" t="n">
-        <v>1.16</v>
+        <v>9.16</v>
       </c>
       <c r="N66" t="n">
         <v>3.94</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>11.46</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45793</v>
+        <v>45796</v>
       </c>
       <c r="H67" t="n">
-        <v>503.85</v>
+        <v>515.35</v>
       </c>
       <c r="I67" t="n">
         <v>512.1768815465172</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.16</v>
+        <v>-5.52</v>
       </c>
       <c r="L67" t="n">
         <v>8.01</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>11.06</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="H68" t="n">
-        <v>504.05</v>
+        <v>480.55</v>
       </c>
       <c r="I68" t="n">
         <v>495.1043461015876</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.19</v>
+        <v>-6.75</v>
       </c>
       <c r="L68" t="n">
-        <v>6.06</v>
+        <v>7.05</v>
       </c>
       <c r="M68" t="n">
         <v>2.81</v>
       </c>
       <c r="N68" t="n">
-        <v>3.49</v>
+        <v>4.66</v>
       </c>
       <c r="O68" t="n">
         <v>2.28</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>12.47</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="H69" t="n">
-        <v>525.75</v>
+        <v>532</v>
       </c>
       <c r="I69" t="n">
         <v>529.5501910528883</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K69" t="n">
-        <v>-9.41</v>
+        <v>-10.71</v>
       </c>
       <c r="L69" t="n">
         <v>14.12</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>4</v>
+      </c>
+      <c r="U69" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>7.22</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="H70" t="n">
-        <v>526.95</v>
+        <v>513.65</v>
       </c>
       <c r="I70" t="n">
         <v>515.1391158270362</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.95</v>
+        <v>-3.45</v>
       </c>
       <c r="L70" t="n">
         <v>3.91</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>7.82</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46022</v>
+        <v>46023</v>
       </c>
       <c r="H71" t="n">
-        <v>482.45</v>
+        <v>502</v>
       </c>
       <c r="I71" t="n">
         <v>490.2943066338507</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K71" t="n">
-        <v>6.07</v>
+        <v>2.27</v>
       </c>
       <c r="L71" t="n">
         <v>2.93</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H72" t="n">
-        <v>486.35</v>
+        <v>479.1</v>
       </c>
       <c r="I72" t="n">
         <v>480.0762803820628</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K72" t="n">
-        <v>-3.12</v>
+        <v>-4.56</v>
       </c>
       <c r="L72" t="n">
-        <v>4.51</v>
+        <v>5.17</v>
       </c>
       <c r="M72" t="n">
         <v>0.23</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="H73" t="n">
-        <v>490.05</v>
+        <v>498.65</v>
       </c>
       <c r="I73" t="n">
         <v>497.0885558208666</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K73" t="n">
-        <v>-2.29</v>
+        <v>-4.08</v>
       </c>
       <c r="L73" t="n">
-        <v>4.14</v>
+        <v>5.67</v>
       </c>
       <c r="M73" t="n">
         <v>2.99</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>8.17</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H74" t="n">
-        <v>556.65</v>
+        <v>517.95</v>
       </c>
       <c r="I74" t="n">
         <v>522.9233702012821</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K74" t="n">
-        <v>11.63</v>
+        <v>3.87</v>
       </c>
       <c r="L74" t="n">
         <v>6.85</v>
@@ -4659,7 +5546,7 @@
         <v>4.05</v>
       </c>
       <c r="N74" t="n">
-        <v>4.8</v>
+        <v>6.95</v>
       </c>
       <c r="O74" t="n">
         <v>1.75</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>13.08</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="H75" t="n">
-        <v>557.05</v>
+        <v>576</v>
       </c>
       <c r="I75" t="n">
         <v>567.733592879845</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K75" t="n">
-        <v>-7.55</v>
+        <v>-11.21</v>
       </c>
       <c r="L75" t="n">
-        <v>8.02</v>
+        <v>12.16</v>
       </c>
       <c r="M75" t="n">
         <v>1.47</v>
       </c>
       <c r="N75" t="n">
-        <v>2.72</v>
+        <v>3.4</v>
       </c>
       <c r="O75" t="n">
         <v>-6.95</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4752,22 +5663,22 @@
         <v>10.35</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="H76" t="n">
-        <v>547.4</v>
+        <v>544.2</v>
       </c>
       <c r="I76" t="n">
         <v>547.1637563219747</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K76" t="n">
-        <v>-4.97</v>
+        <v>-5.52</v>
       </c>
       <c r="L76" t="n">
-        <v>5.43</v>
+        <v>6.25</v>
       </c>
       <c r="M76" t="n">
         <v>1.57</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4833,6 +5756,14 @@
       <c r="Q77" t="n">
         <v>79</v>
       </c>
+      <c r="R77" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9791,7 +10722,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54.4</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="6">
@@ -9801,7 +10732,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -9811,7 +10742,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="8">
@@ -9821,7 +10752,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -9831,7 +10762,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -9841,7 +10772,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101.6</v>
+        <v>102.6</v>
       </c>
     </row>
     <row r="11">
@@ -9851,7 +10782,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -9861,7 +10792,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
@@ -9871,7 +10802,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>42.7</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="14">
@@ -9881,7 +10812,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7.85</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="15">
@@ -9891,7 +10822,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.68</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="16">
@@ -9901,7 +10832,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.22</v>
+        <v>-5.05</v>
       </c>
     </row>
     <row r="17">
@@ -9911,7 +10842,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>620.85</v>
+        <v>584.86</v>
       </c>
     </row>
     <row r="18">
@@ -9921,7 +10852,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -9931,7 +10862,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.970000000000001</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="20">
@@ -9941,7 +10872,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8.09</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="21">
@@ -9951,7 +10882,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29</v>
+        <v>31.57</v>
       </c>
     </row>
     <row r="22">
@@ -9961,7 +10892,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23">
@@ -9971,7 +10902,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
@@ -9981,7 +10912,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="25">
@@ -9991,7 +10922,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.09</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="26">
@@ -10001,7 +10932,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.42</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="27">
@@ -10011,7 +10942,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.75</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
@@ -10021,7 +10952,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29">
